--- a/Result/12-12-24/NASDAQstock_12-12-24period252RS90.xlsx
+++ b/Result/12-12-24/NASDAQstock_12-12-24period252RS90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kelvinyue/Desktop/Coding project/StockAnalysis/Result/12-12-24/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A446DE1-6853-B646-8B1E-71AF6CD7CDC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94CB18-1E0F-FD40-BAA4-A978AD6D90A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
